--- a/reports/scan/fs_media_studio_fs.xlsx
+++ b/reports/scan/fs_media_studio_fs.xlsx
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -637,9 +637,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
@@ -699,9 +699,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -714,9 +714,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -791,9 +791,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -868,9 +868,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -992,74 +992,74 @@
           <t>shoots/SHOOT-2026-A/brief.txt</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1084,9 +1084,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1300,74 +1300,74 @@
           <t>shoots/SHOOT-2026-B/brief.txt</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1392,9 +1392,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1561,9 +1561,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
@@ -1859,16 +1859,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1936,16 +1936,16 @@
           <t>16</t>
         </is>
       </c>
-      <c r="F20" s="5" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
           <t>16</t>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2018,9 +2018,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2095,9 +2095,9 @@
           <t>24</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">

--- a/reports/scan/fs_media_studio_fs.xlsx
+++ b/reports/scan/fs_media_studio_fs.xlsx
@@ -532,72 +532,72 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -622,9 +622,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -776,9 +776,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -853,9 +853,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -992,74 +992,74 @@
           <t>shoots/SHOOT-2026-A/brief.txt</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1084,9 +1084,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1300,74 +1300,74 @@
           <t>shoots/SHOOT-2026-B/brief.txt</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1392,9 +1392,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
@@ -1581,9 +1581,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>24</t>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1610,72 +1610,72 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
@@ -1864,9 +1864,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>24</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="G22" s="5" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2466,7 +2466,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">

--- a/reports/scan/fs_media_studio_fs.xlsx
+++ b/reports/scan/fs_media_studio_fs.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -888,9 +888,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>16</t>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1581,9 +1581,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
@@ -1658,9 +1658,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
@@ -1735,9 +1735,9 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>24</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
@@ -1864,9 +1864,9 @@
           <t>36</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>36</t>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>48</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>32</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
@@ -2092,12 +2092,12 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>24</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
